--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260930.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260930.xlsx
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>147,294,508</t>
+          <t>22,470,204</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>22,470,204</t>
+          <t>147,294,508</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
